--- a/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案0930_rev2.xlsx
+++ b/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案0930_rev2.xlsx
@@ -575,7 +575,7 @@
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>未確定事項の確認先: 内閣府＝林副大臣の使用言語・通訳方式。ADRC＝評価フォーム（用意・URL/QR）、RT の質問方式、Co-Moderator の要否。Sylvia（SCDF/COSEM）＝Commissioner の出席、Closing の SCDF 登壇者、フィールドトリップ集合場所、会場バナー前の写真。</t>
+          <t>未確定事項の確認先（内閣府分は 9/30 確定: 林副大臣は英語で挨拶、肩書 Deputy Minister for Disaster Management, Cabinet Office of Japan、Gala 欠席）。ADRC＝評価フォーム（用意・URL/QR）、RT の質問方式、Co-Moderator の要否。Sylvia（SCDF/COSEM）＝Commissioner の出席、Closing の SCDF 登壇者、フィールドトリップ集合場所、会場バナー前の写真。</t>
         </is>
       </c>
     </row>
@@ -1232,19 +1232,19 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>Lastly, I am pleased to invite Mr HAYASHI Masamichi, Deputy Minister, Cabinet Office of Japan (COJ), to deliver his opening remarks. Deputy Minister Hayashi, please.
+          <t>Lastly, I am pleased to invite Mr HAYASHI Masamichi, Deputy Minister for Disaster Management, Cabinet Office of Japan (COJ), to deliver his opening remarks. Deputy Minister Hayashi, please.
 （挨拶 4〜5分）
 Thank you very much, Deputy Minister Hayashi.</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>逐次通訳を入れると所要が倍になる。日本語で話す場合は英訳原稿を事前配布し通訳は要点のみ、または英語原稿の読み上げ。使用言語・通訳の方式は内閣府に確認【TBC・ADRC→内閣府】。挨拶後、林副大臣は Japan 席に着席、その後退席（Japan 席は内閣府参事官に交代）。</t>
+          <t>英語で挨拶（内閣府確認済、児玉 9/30）。通訳なし。肩書は Deputy Minister for Disaster Management, Cabinet Office of Japan（内閣府確認済）。挨拶後、林副大臣は Japan 席に着席、その後退席（Japan 席は内閣府参事官に交代）。副大臣は 28 日 22:20 発で帰国、Gala は欠席（御手洗参事官が短時間出席）。</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Deputy Minister（演台）＋通訳</t>
+          <t>Deputy Minister（演台）</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>演台マイク（通訳用ハンド1）</t>
+          <t>演台マイク</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -5367,7 +5367,7 @@
           <t>Opening Remarks (order per SCDF, tbc):
 – Prof. MIURA Fusanori, Chairman, Asian Disaster Reduction Center
 – Mr Eric Yap Wee Teck, Commissioner, Singapore Civil Defence Force (tbc)
-– Mr HAYASHI Masamichi, Deputy Minister, Cabinet Office of Japan (COJ)
+– Mr HAYASHI Masamichi, Deputy Minister for Disaster Management, Cabinet Office of Japan (COJ)
 Emcee: LTC Chen Yong Kai, SCDF</t>
         </is>
       </c>

--- a/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案0930_rev2.xlsx
+++ b/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案0930_rev2.xlsx
@@ -528,7 +528,7 @@
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>・時間配分: 開会挨拶は三浦 約3分・Commissioner 5分・林 4〜5分・MC 計2分（15分枠、Sylvia 9/30 要望に基づく暫定）。
+          <t>・時間配分: 開会挨拶は三浦 3〜4分・Commissioner 5分・林 4〜5分・MC 計2分（15分枠、Sylvia 9/30 要望に基づく暫定。三浦原稿は案1001r＝約4分、3分版は削除候補あり）。
 ・ADRC Opening 登壇順＝三浦センター長 → Commissioner（tbc） → 林副大臣（暫定。後の登壇者ほど上位とするシンガポール側プロトコルを尊重、Sylvia に確認中）。RT はメンバー国 各5分まで（荒木田 9/29 決定、ベル方式）、アドバイザー国・ADPC・その他機関は3分（仮）。TS は rev1.0（紹介5分＋発表15分×6枠＋質疑15分＋まとめ10分）。</t>
         </is>
       </c>
@@ -1091,13 +1091,13 @@
       <c r="F12" s="7" t="inlineStr">
         <is>
           <t>To formally start the programme, may I invite Professor MIURA Fusanori, Chairman of the Asian Disaster Reduction Center, to deliver his welcome remarks. Professor Miura, please.
-（挨拶 約3分：別紙 Opening Remarks 案 rev3）
+（挨拶 約4分：別紙 Opening Remarks 案1001r〈児玉修正反映〉。3分に詰める場合の削除候補は原稿末尾）
 Thank you very much, Professor Miura.</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>原稿: ACDR2026_Opening_Remarks_MIURA_案0929.docx rev3（英語読み上げ、3分＝約340語）。Sylvia 9/30（児玉経由）: Commissioner 5分、Chairman は短めの要望。4分版に戻す場合は原稿末尾の注記参照。</t>
+          <t>原稿: ACDR2026_Opening_Remarks_MIURA_案1001r.docx（児玉修正案 10/1 を反映、英語約540語＝約4分。3分版は原稿末尾の削除候補で対応）。Sylvia 9/30（児玉経由）: Commissioner 5分、Chairman は短めの要望。4分版に戻す場合は原稿末尾の注記参照。</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>原稿: ACDR2026_Closing_Remarks_MIURA_案0929.docx（約3分）。次回 ACDR は仙台開催、APMCDRR と back-to-back、2027年10月（挨拶内で発表）。</t>
+          <t>原稿: ACDR2026_Closing_Remarks_MIURA_案1001_rev2.docx（サマリー重複を削除、約280語＝2分強）（約3分）。次回 ACDR は仙台開催、APMCDRR と back-to-back、2027年10月（挨拶内で発表）。</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">

--- a/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案0930_rev2.xlsx
+++ b/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案0930_rev2.xlsx
@@ -529,7 +529,7 @@
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>・時間配分: 開会挨拶は三浦 3〜4分・Commissioner 5分・林 4〜5分・MC 計2分（15分枠、Sylvia 9/30 要望に基づく暫定。三浦原稿は案1001r＝約4分、3分版は削除候補あり）。
-・ADRC Opening 登壇順＝三浦センター長 → Commissioner（tbc） → 林副大臣（暫定。後の登壇者ほど上位とするシンガポール側プロトコルを尊重、Sylvia に確認中）。RT はメンバー国 各5分まで（荒木田 9/29 決定、ベル方式）、アドバイザー国・ADPC・その他機関は3分（仮）。TS は rev1.0（紹介5分＋発表15分×6枠＋質疑15分＋まとめ10分）。</t>
+・ADRC Opening 登壇順＝三浦センター長 → Commissioner（tbc） → 林副大臣（暫定。後の登壇者ほど上位とするシンガポール側プロトコルを尊重、Sylvia に確認中）。RT はメンバー国 各5分まで（荒木田 9/29 決定、ベル方式）、アドバイザー国・ADPC・その他機関は4分（荒木田 10/1 決定。吉田は機関 5分を提案、登録者数次第で再調整）。TS は rev1.0（紹介5分＋発表15分×6枠＋質疑15分＋まとめ10分）。</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       <c r="F17" s="7" t="inlineStr">
         <is>
           <t>Excellencies, distinguished delegates. The Roundtable is the session where ADRC member countries and partners share, in their own words, the progress they have made under the Sendai Framework for Disaster Risk Reduction and the challenges that remain as we approach 2030. Part 1 is held this afternoon and Part 2 will be held tomorrow morning at 9 o’clock.
-In the interest of time, may I remind you of the following guidance: i) Time allotted for member countries is 5 minutes, and for adviser countries and partner organisations 3 minutes; ii) The sequence will be alphabetical order, starting from member countries; iii) Please speak from your seat using the table microphone; iv) A bell will ring once when one minute remains, twice at thirty seconds, and three times at the end of your time. Please observe these to keep the programme on schedule; v) Questions and comments will not be taken on the floor during the statements; please write them on the comment sheet at your seat [or submit them via the online form shown on the screen]. These will be shared with the speakers and reflected in the conference summary.</t>
+In the interest of time, may I remind you of the following guidance: i) Time allotted for member countries is 5 minutes, and for adviser countries and partner organisations 4 minutes; ii) The sequence will be alphabetical order, starting from member countries; iii) Please speak from your seat using the table microphone; iv) A bell will ring once when one minute remains, twice at thirty seconds, and three times at the end of your time. Please observe these to keep the programme on schedule; v) Questions and comments will not be taken on the floor during the statements; please write them on the comment sheet at your seat [or submit them via the online form shown on the screen]. These will be shared with the speakers and reflected in the conference summary. If time allows at the end of each part, we will take a few questions from the floor.</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -3481,7 +3481,7 @@
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>残り2か国（Uzbekistan, Viet Nam、各5分）→ アドバイザー国（希望があれば）→ ADPC → その他機関アルファベット順（ADB, AHA Centre, Google, オンライン）各3分 → まとめ。全員が発言すると約5分超過。未登録分が緩衝。</t>
+          <t>残り2か国（Uzbekistan, Viet Nam、各5分）→ アドバイザー国（希望があれば）→ ADPC → その他機関アルファベット順（ADB, AHA Centre, Google, オンライン）各4分 → まとめ。全員が発言すると 09:36 頃までかかり約6分超過。未登録分（オンライン等）が緩衝。超過分は TS まとめ（10分）で吸収。</t>
         </is>
       </c>
       <c r="G6" s="6" t="n"/>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Good morning, Excellencies, distinguished delegates. Welcome to the second part of the Roundtable Session. Let us hear the remaining statements. For guidance, member countries are allotted 5 minutes while adviser countries and partner organisations are allotted 3 minutes each. Kindly wind up when the third bell rings.</t>
+          <t>Good morning, Excellencies, distinguished delegates. Welcome to the second part of the Roundtable Session. Let us hear the remaining statements. For guidance, member countries are allotted 5 minutes while adviser countries and partner organisations are allotted 4 minutes each. Kindly wind up when the third bell rings.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -3717,8 +3717,8 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the National Emergency Management Agency of New Zealand. You have three minutes, please.
-（ステートメント 3分）
+          <t>Next, I would like to invite the National Emergency Management Agency of New Zealand. You have four minutes, please.
+（ステートメント 4分）
 Thank you very much.</t>
         </is>
       </c>
@@ -3777,7 +3777,7 @@
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -3792,8 +3792,8 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the Asian Disaster Preparedness Center, ADPC. You have three minutes, please.
-（ステートメント 3分）
+          <t>Next, I would like to invite the Asian Disaster Preparedness Center, ADPC. You have four minutes, please.
+（ステートメント 4分）
 Thank you very much.</t>
         </is>
       </c>
@@ -3852,7 +3852,7 @@
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -3867,8 +3867,8 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the Asian Development Bank, ADB. You have three minutes, please.
-（ステートメント 3分）
+          <t>Next, I would like to invite the Asian Development Bank, ADB. You have four minutes, please.
+（ステートメント 4分）
 Thank you very much.</t>
         </is>
       </c>
@@ -3927,7 +3927,7 @@
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -3942,8 +3942,8 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite the AHA Centre. You have three minutes, please.
-（ステートメント 3分）
+          <t>Next, I would like to invite the AHA Centre. You have four minutes, please.
+（ステートメント 4分）
 Thank you very much.</t>
         </is>
       </c>
@@ -4002,7 +4002,7 @@
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -4017,8 +4017,8 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite Google. You have three minutes, please.
-（ステートメント 3分）
+          <t>Next, I would like to invite Google. You have four minutes, please.
+（ステートメント 4分）
 Thank you very much.</t>
         </is>
       </c>
@@ -4077,7 +4077,7 @@
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -4092,8 +4092,8 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Next, I would like to invite online participants [UNDP / WMO]. You have three minutes, please.
-（ステートメント 3分）
+          <t>Next, I would like to invite online participants [UNDP / WMO]. You have four minutes, please.
+（ステートメント 4分）
 Thank you very much.</t>
         </is>
       </c>
@@ -4152,7 +4152,7 @@
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Instruction for Speakers – Time Allocation: Member countries maximum 5 minutes; adviser countries and partner organisations maximum 3 minutes
+          <t>Instruction for Speakers – Time Allocation: Member countries maximum 5 minutes; adviser countries and partner organisations maximum 4 minutes
 First ring: 1 minute left / Second ring: 30 seconds left / Third ring: end of statement</t>
         </is>
       </c>

--- a/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案0930_rev2.xlsx
+++ b/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案0930_rev2.xlsx
@@ -506,7 +506,8 @@
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>・会場: Peridot 201-203, Singapore EXPO。使用言語: 英語。Zoom Webinar による双方向ハイブリッド（オンライン登壇の可能性: UNDP・WMO＝未登録）。AI通訳（日本語）は神戸側が監視。</t>
+          <t>・会場: Peridot 201-203, Singapore EXPO。使用言語: 英語。Zoom Webinar による双方向ハイブリッド（オンライン登壇の可能性: UNDP・WMO＝未登録）。AI通訳（日本語）は神戸側が監視。
+・AI 翻訳字幕＝ポケトークライブ（Sentio）。参加者はスマホで QR（PPT 08 に掲示）を読み、各自の言語で字幕を見る。制約: 1 セッション連続 3 時間まで（1 日 3 時間ではない）。→ 28 日は 12:35 に開始（15:00 の RT 終了まで 2 時間 25 分）。SC で使う場合は 15:10 に再起動して新しい QR を SC のスライドに出す。29 日は 08:55 に開始（11:30 の TS 終了まで 2 時間 35 分）、11:35 に再起動して閉会（11:45-12:00）用の新 QR を PPT 20 に出す。08:00 の接続テストでは本番セッションを立ち上げない（テストは別セッションで行い終了する）。担当: 現地一次対応 藤本、設定 中村（神戸）。</t>
         </is>
       </c>
     </row>
@@ -899,7 +900,7 @@
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>昼食（Hall 3, 11:45-12:45）から参加者がPeridotへ戻る。VIP（Commissioner、林副大臣、三浦センター長）は12:40までに着席。</t>
+          <t>昼食（Hall 3, 11:45-12:45）から参加者がPeridotへ戻る。VIP（Commissioner、林副大臣、三浦センター長）は12:40までに着席。12:35 ポケトークライブ（Sentio）の本番セッションを開始（連続 3 時間上限。15:00 まで持つ）。QR は PPT 08 とテーブル上の案内カードで掲示。</t>
         </is>
       </c>
       <c r="G8" s="6" t="n"/>
@@ -3390,7 +3391,7 @@
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>入室 08:00（Expo 最早）。机・椅子の配置は 28 日から変えない（前方登壇者卓・演台は 28 日設営のまま。29 日朝は家具移動なし）。AV のみ: 前方卓のマイク（最大8）の通電、持込カメラと Zoom 接続、演台 PC・クリッカー・返しモニター、登壇者集合 08:30（池田）、スライド集約。</t>
+          <t>入室 08:00（Expo 最早）。08:55 ポケトークライブ（Sentio）の本番セッションを開始（連続 3 時間上限、11:30 の TS 終了まで持つ。テスト用セッションは 08:50 までに終了）。机・椅子の配置は 28 日から変えない（前方登壇者卓・演台は 28 日設営のまま。29 日朝は家具移動なし）。AV のみ: 前方卓のマイク（最大8）の通電、持込カメラと Zoom 接続、演台 PC・クリッカー・返しモニター、登壇者集合 08:30（池田）、スライド集約。</t>
         </is>
       </c>
       <c r="G4" s="6" t="n"/>
@@ -4930,7 +4931,7 @@
       <c r="E28" s="6" t="n"/>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>所要15分。Summary（宮木所長＝Executive Director）6分＋閉会挨拶 2名×3分（三浦センター長＝Chairman、SCDF 代表【TBC】）＋MC連絡3分。</t>
+          <t>所要15分。11:35 にポケトークライブを再起動し、新しい QR を PPT 20 に掲示（前セッションは 08:55 開始のため 11:55 で 3 時間に達する）。Summary（宮木所長＝Executive Director）6分＋閉会挨拶 2名×3分（三浦センター長＝Chairman、SCDF 代表【TBC】）＋MC連絡3分。</t>
         </is>
       </c>
       <c r="G28" s="6" t="n"/>

--- a/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案0930_rev2.xlsx
+++ b/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案0930_rev2.xlsx
@@ -507,7 +507,7 @@
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>・会場: Peridot 201-203, Singapore EXPO。使用言語: 英語。Zoom Webinar による双方向ハイブリッド（オンライン登壇の可能性: UNDP・WMO＝未登録）。AI通訳（日本語）は神戸側が監視。
-・AI 翻訳字幕＝ポケトークライブ（Sentio）。参加者はスマホで QR（PPT 08 に掲示）を読み、各自の言語で字幕を見る。制約: 1 セッション連続 3 時間まで（1 日 3 時間ではない）。→ 28 日は 12:35 に開始（15:00 の RT 終了まで 2 時間 25 分）。SC で使う場合は 15:10 に再起動して新しい QR を SC のスライドに出す。29 日は 08:55 に開始（11:30 の TS 終了まで 2 時間 35 分）、11:35 に再起動して閉会（11:45-12:00）用の新 QR を PPT 20 に出す。08:00 の接続テストでは本番セッションを立ち上げない（テストは別セッションで行い終了する）。担当: 現地一次対応 藤本、設定 中村（神戸）。</t>
+・AI 翻訳字幕＝ポケトークライブ（Sentio）。参加者はスマホで QR（PPT 08 に掲示）を読み、各自の言語で字幕を見る。制約: 1 セッション 90 分まで（荒木田 10/1 訂正。1 日の上限ではない）。セッションごとにゲスト URL が変わる前提で、再起動のたびに新 QR を掲示し MC が再読込みを案内（同一 URL を維持できるかは荒木田がツール側で確認）。→ 28 日: S1 12:40 開始（〜14:10）、S2 14:08 に再起動（13 番目の発言者の後、20 秒の案内）、〜15:38 で RT 終了 15:00 をカバー。SC で使う場合は S3 15:12。29 日: S1 08:55（〜10:25、RT2 と TS 発表 3 件目まで）、S2 10:20 に再起動（発表 3 件目と 4 件目の間）、〜11:50 で質疑・まとめをカバー、S3 11:40 に再起動（コーヒーブレイク中）で閉会 11:45-12:00 をカバー。08:00 の接続テストは別セッションで行い本番前に終了。担当: 現地一次対応 藤本、設定 中村（神戸）。</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>昼食（Hall 3, 11:45-12:45）から参加者がPeridotへ戻る。VIP（Commissioner、林副大臣、三浦センター長）は12:40までに着席。12:35 ポケトークライブ（Sentio）の本番セッションを開始（連続 3 時間上限。15:00 まで持つ）。QR は PPT 08 とテーブル上の案内カードで掲示。</t>
+          <t>昼食（Hall 3, 11:45-12:45）から参加者がPeridotへ戻る。VIP（Commissioner、林副大臣、三浦センター長）は12:40までに着席。12:40 ポケトークライブ（Sentio）の本番セッション S1 を開始（1 セッション 90 分上限 → 14:10 まで。14:08 に S2 へ再起動）。QR は PPT 08 とテーブル上の案内カードで掲示。</t>
         </is>
       </c>
       <c r="G8" s="6" t="n"/>
@@ -1355,7 +1355,7 @@
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>Moderator: SCDF（LTC Chen Yong Kai）単独（Co-Moderator は置かない: Gerry・吉田 9/30 合意、2025 も喜多参事官単独）。ADRC 運営: 吉田（PIC・進行補助・ベル）、Gerry（ノート・サマリー）、池田（PC・スクリーン）、荒木田（AV/Zoom）。</t>
+          <t>【ポケトークライブ】S1 は 14:10 で 90 分に達するため、13 番目の発言者（14:03-14:08 枠）の後に藤本が S2 を起動し、池田が新 QR スライド（PPT 08b）を 20 秒表示、MC が「Please scan the new QR code for live translation」と一言。Moderator: SCDF（LTC Chen Yong Kai）単独（Co-Moderator は置かない: Gerry・吉田 9/30 合意、2025 も喜多参事官単独）。ADRC 運営: 吉田（PIC・進行補助・ベル）、Gerry（ノート・サマリー）、池田（PC・スクリーン）、荒木田（AV/Zoom）。</t>
         </is>
       </c>
       <c r="G16" s="6" t="n"/>
@@ -3391,7 +3391,7 @@
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>入室 08:00（Expo 最早）。08:55 ポケトークライブ（Sentio）の本番セッションを開始（連続 3 時間上限、11:30 の TS 終了まで持つ。テスト用セッションは 08:50 までに終了）。机・椅子の配置は 28 日から変えない（前方登壇者卓・演台は 28 日設営のまま。29 日朝は家具移動なし）。AV のみ: 前方卓のマイク（最大8）の通電、持込カメラと Zoom 接続、演台 PC・クリッカー・返しモニター、登壇者集合 08:30（池田）、スライド集約。</t>
+          <t>入室 08:00（Expo 最早）。08:55 ポケトークライブ（Sentio）の本番セッション S1 を開始（90 分上限 → 10:25 まで。10:20 に S2、11:40 に S3 へ再起動。テスト用セッションは 08:50 までに終了）。机・椅子の配置は 28 日から変えない（前方登壇者卓・演台は 28 日設営のまま。29 日朝は家具移動なし）。AV のみ: 前方卓のマイク（最大8）の通電、持込カメラと Zoom 接続、演台 PC・クリッカー・返しモニター、登壇者集合 08:30（池田）、スライド集約。</t>
         </is>
       </c>
       <c r="G4" s="6" t="n"/>
@@ -4224,7 +4224,7 @@
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Moderator: LTC Chen Yong Kai（SCDF）。Co-Chair: Dr. Mizan Bisri（ADRC/ADPC）。PIC: 池田。AV/Zoom: 荒木田。カメラ・フロア: 塩見。配分（rev1.0）: 紹介5分＋発表15分×6＋質疑15分＋まとめ10分。</t>
+          <t>【ポケトークライブ】S1 は 10:25 で 90 分に達するため、発表 3 件目（10:05-10:20）の後に S2 を起動し、新 QR スライド（PPT 16b）を 20 秒表示、Moderator が再読込みを案内。Moderator: LTC Chen Yong Kai（SCDF）。Co-Chair: Dr. Mizan Bisri（ADRC/ADPC）。PIC: 池田。AV/Zoom: 荒木田。カメラ・フロア: 塩見。配分（rev1.0）: 紹介5分＋発表15分×6＋質疑15分＋まとめ10分。</t>
         </is>
       </c>
       <c r="G17" s="6" t="n"/>
@@ -4931,7 +4931,7 @@
       <c r="E28" s="6" t="n"/>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>所要15分。11:35 にポケトークライブを再起動し、新しい QR を PPT 20 に掲示（前セッションは 08:55 開始のため 11:55 で 3 時間に達する）。Summary（宮木所長＝Executive Director）6分＋閉会挨拶 2名×3分（三浦センター長＝Chairman、SCDF 代表【TBC】）＋MC連絡3分。</t>
+          <t>所要15分。11:40 にポケトークライブを S3 に再起動し、新しい QR を PPT 20 に掲示（S2 は 10:20 開始のため 11:50 で 90 分に達する）。Summary（宮木所長＝Executive Director）6分＋閉会挨拶 2名×3分（三浦センター長＝Chairman、SCDF 代表【TBC】）＋MC連絡3分。</t>
         </is>
       </c>
       <c r="G28" s="6" t="n"/>

--- a/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案0930_rev2.xlsx
+++ b/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案0930_rev2.xlsx
@@ -507,7 +507,7 @@
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>・会場: Peridot 201-203, Singapore EXPO。使用言語: 英語。Zoom Webinar による双方向ハイブリッド（オンライン登壇の可能性: UNDP・WMO＝未登録）。AI通訳（日本語）は神戸側が監視。
-・AI 翻訳字幕＝ポケトークライブ（Sentio）。参加者はスマホで QR（PPT 08 に掲示）を読み、各自の言語で字幕を見る。制約: 1 セッション 90 分まで（荒木田 10/1 訂正。1 日の上限ではない）。セッションごとにゲスト URL が変わる前提で、再起動のたびに新 QR を掲示し MC が再読込みを案内（同一 URL を維持できるかは荒木田がツール側で確認）。→ 28 日: S1 12:40 開始（〜14:10）、S2 14:08 に再起動（13 番目の発言者の後、20 秒の案内）、〜15:38 で RT 終了 15:00 をカバー。SC で使う場合は S3 15:12。29 日: S1 08:55（〜10:25、RT2 と TS 発表 3 件目まで）、S2 10:20 に再起動（発表 3 件目と 4 件目の間）、〜11:50 で質疑・まとめをカバー、S3 11:40 に再起動（コーヒーブレイク中）で閉会 11:45-12:00 をカバー。08:00 の接続テストは別セッションで行い本番前に終了。担当: 現地一次対応 藤本、設定 中村（神戸）。</t>
+・AI 翻訳字幕＝ポケトークライブ（Sentio）。参加者はスマホで QR（PPT 08 に掲示）を読み、各自の言語で字幕を見る。仕様（プレミアムプラン、pocketalk.jp/sentio/lineup・取扱説明書 10/1 確認）: 通訳の連続利用は 1 回 90 分、月の累計は無制限、共有可能人数 50 名、共有 URL/QR は共有開始から 6 時間で自動破棄。カンファレンスプランは連続無制限・URL 固定・50 名超も可（見積り制、リハーサル無償）。→ 運用: 通訳は 90 分ごとに藤本が再開（28 日 14:08 頃＝RT 13 番目の発言者の後、29 日 10:20 頃＝TS 発表 3 と 4 の間、11:40 頃＝閉会前）。共有 URL は本番用を 28 日 12:40、29 日 08:55 に開始する（08:00 の接続テストで開いた共有は必ず終了。6 時間で URL が破棄されるため、テストの共有をそのまま使うと 14:00 頃に切れる）。通訳を再開しても同じ共有 URL が維持されるかは神戸のリハーサルで検証（維持されるなら QR の再掲示は不要。されない場合は再開時に新 QR＝PPT 08b／16b を 20 秒表示し MC が再読込みを案内）。同時閲覧 50 名を超える見込み（日本語字幕の需要が多い場合）ならカンファレンスプランの見積りを取る。担当: 現地一次対応 藤本、設定 中村（神戸）。</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>昼食（Hall 3, 11:45-12:45）から参加者がPeridotへ戻る。VIP（Commissioner、林副大臣、三浦センター長）は12:40までに着席。12:40 ポケトークライブ（Sentio）の本番セッション S1 を開始（1 セッション 90 分上限 → 14:10 まで。14:08 に S2 へ再起動）。QR は PPT 08 とテーブル上の案内カードで掲示。</t>
+          <t>昼食（Hall 3, 11:45-12:45）から参加者がPeridotへ戻る。VIP（Commissioner、林副大臣、三浦センター長）は12:40までに着席。12:40 ポケトークライブ（Sentio）の本番の共有 URL を開始し通訳を開始（共有 URL は 6 時間有効、通訳は 90 分で再開が必要 → 14:08 頃に再開）。QR は PPT 08 とテーブル上の案内カードで掲示。</t>
         </is>
       </c>
       <c r="G8" s="6" t="n"/>
@@ -1355,7 +1355,7 @@
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>【ポケトークライブ】S1 は 14:10 で 90 分に達するため、13 番目の発言者（14:03-14:08 枠）の後に藤本が S2 を起動し、池田が新 QR スライド（PPT 08b）を 20 秒表示、MC が「Please scan the new QR code for live translation」と一言。Moderator: SCDF（LTC Chen Yong Kai）単独（Co-Moderator は置かない: Gerry・吉田 9/30 合意、2025 も喜多参事官単独）。ADRC 運営: 吉田（PIC・進行補助・ベル）、Gerry（ノート・サマリー）、池田（PC・スクリーン）、荒木田（AV/Zoom）。</t>
+          <t>【ポケトークライブ】通訳は 12:40 開始分が 14:10 で 90 分に達するため、13 番目の発言者（14:03-14:08 枠）の後に藤本が通訳を再開。共有 URL が維持されない場合のみ、池田が新 QR スライド（PPT 08b）を 20 秒表示し MC が「Please scan the new QR code for live translation」と一言。Moderator: SCDF（LTC Chen Yong Kai）単独（Co-Moderator は置かない: Gerry・吉田 9/30 合意、2025 も喜多参事官単独）。ADRC 運営: 吉田（PIC・進行補助・ベル）、Gerry（ノート・サマリー）、池田（PC・スクリーン）、荒木田（AV/Zoom）。</t>
         </is>
       </c>
       <c r="G16" s="6" t="n"/>
@@ -3391,7 +3391,7 @@
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>入室 08:00（Expo 最早）。08:55 ポケトークライブ（Sentio）の本番セッション S1 を開始（90 分上限 → 10:25 まで。10:20 に S2、11:40 に S3 へ再起動。テスト用セッションは 08:50 までに終了）。机・椅子の配置は 28 日から変えない（前方登壇者卓・演台は 28 日設営のまま。29 日朝は家具移動なし）。AV のみ: 前方卓のマイク（最大8）の通電、持込カメラと Zoom 接続、演台 PC・クリッカー・返しモニター、登壇者集合 08:30（池田）、スライド集約。</t>
+          <t>入室 08:00（Expo 最早）。08:55 ポケトークライブ（Sentio）の本番の共有 URL を開始し通訳を開始（通訳は 90 分で再開が必要 → 10:20 頃と 11:40 頃に再開。テスト時の共有は 08:50 までに終了しておく）。机・椅子の配置は 28 日から変えない（前方登壇者卓・演台は 28 日設営のまま。29 日朝は家具移動なし）。AV のみ: 前方卓のマイク（最大8）の通電、持込カメラと Zoom 接続、演台 PC・クリッカー・返しモニター、登壇者集合 08:30（池田）、スライド集約。</t>
         </is>
       </c>
       <c r="G4" s="6" t="n"/>
@@ -4224,7 +4224,7 @@
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>【ポケトークライブ】S1 は 10:25 で 90 分に達するため、発表 3 件目（10:05-10:20）の後に S2 を起動し、新 QR スライド（PPT 16b）を 20 秒表示、Moderator が再読込みを案内。Moderator: LTC Chen Yong Kai（SCDF）。Co-Chair: Dr. Mizan Bisri（ADRC/ADPC）。PIC: 池田。AV/Zoom: 荒木田。カメラ・フロア: 塩見。配分（rev1.0）: 紹介5分＋発表15分×6＋質疑15分＋まとめ10分。</t>
+          <t>【ポケトークライブ】通訳は 08:55 開始分が 10:25 で 90 分に達するため、発表 3 件目（10:05-10:20）の後に藤本が通訳を再開。共有 URL が維持されない場合のみ新 QR スライド（PPT 16b）を 20 秒表示し Moderator が再読込みを案内。Moderator: LTC Chen Yong Kai（SCDF）。Co-Chair: Dr. Mizan Bisri（ADRC/ADPC）。PIC: 池田。AV/Zoom: 荒木田。カメラ・フロア: 塩見。配分（rev1.0）: 紹介5分＋発表15分×6＋質疑15分＋まとめ10分。</t>
         </is>
       </c>
       <c r="G17" s="6" t="n"/>
@@ -4931,7 +4931,7 @@
       <c r="E28" s="6" t="n"/>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>所要15分。11:40 にポケトークライブを S3 に再起動し、新しい QR を PPT 20 に掲示（S2 は 10:20 開始のため 11:50 で 90 分に達する）。Summary（宮木所長＝Executive Director）6分＋閉会挨拶 2名×3分（三浦センター長＝Chairman、SCDF 代表【TBC】）＋MC連絡3分。</t>
+          <t>所要15分。11:40 頃にポケトークライブの通訳を再開（10:20 再開分が 11:50 で 90 分に達するため）。共有 URL が維持されない場合のみ新 QR を PPT 20 に掲示。Summary（宮木所長＝Executive Director）6分＋閉会挨拶 2名×3分（三浦センター長＝Chairman、SCDF 代表【TBC】）＋MC連絡3分。</t>
         </is>
       </c>
       <c r="G28" s="6" t="n"/>
